--- a/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04645</v>
+        <v>0.06565</v>
       </c>
       <c r="E2">
-        <v>0.05890000000000001</v>
+        <v>0.07645</v>
       </c>
       <c r="F2">
-        <v>0.205</v>
+        <v>0.1665</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7495</v>
+        <v>7916</v>
       </c>
       <c r="L2">
-        <v>0.4553767262696778</v>
+        <v>0.453706569460206</v>
       </c>
       <c r="M2">
-        <v>3151.9946</v>
+        <v>4756.0656</v>
       </c>
       <c r="N2">
-        <v>0.03297713985595493</v>
+        <v>0.04597586783570331</v>
       </c>
       <c r="O2">
-        <v>0.4205463108739159</v>
+        <v>0.6008167761495705</v>
       </c>
       <c r="P2">
-        <v>3151.9946</v>
+        <v>4022.8656</v>
       </c>
       <c r="Q2">
-        <v>0.03297713985595493</v>
+        <v>0.03888818042089186</v>
       </c>
       <c r="R2">
-        <v>0.4205463108739159</v>
+        <v>0.5081942395149065</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>733.2000000000003</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1541610359621617</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>35856.4</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.3466161415990797</v>
       </c>
       <c r="W2">
-        <v>0.1074465829320094</v>
+        <v>0.1092347466432134</v>
       </c>
       <c r="X2">
-        <v>0.05925300619142107</v>
+        <v>0.0910922812571236</v>
       </c>
       <c r="Y2">
-        <v>0.04819357674058829</v>
+        <v>0.0181424653860898</v>
       </c>
       <c r="Z2">
-        <v>0.09120454568123711</v>
+        <v>0.1188048830976402</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0390113743188575</v>
+        <v>0.06324545953403019</v>
       </c>
       <c r="AC2">
-        <v>-0.0390113743188575</v>
+        <v>-0.06324545953403019</v>
       </c>
       <c r="AD2">
-        <v>106329.9</v>
+        <v>130639.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>106329.9</v>
+        <v>130639.9</v>
       </c>
       <c r="AG2">
-        <v>106329.9</v>
+        <v>94783.5</v>
       </c>
       <c r="AH2">
-        <v>0.5266174073639339</v>
+        <v>0.5580829170705409</v>
       </c>
       <c r="AI2">
-        <v>0.590581239571924</v>
+        <v>0.6514136494799508</v>
       </c>
       <c r="AJ2">
-        <v>0.5266174073639339</v>
+        <v>0.4781479136661614</v>
       </c>
       <c r="AK2">
-        <v>0.590581239571924</v>
+        <v>0.5755201075462728</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0626</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="E3">
-        <v>0.08220000000000001</v>
+        <v>0.0901</v>
       </c>
       <c r="F3">
-        <v>0.196</v>
+        <v>0.162</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4734.3</v>
+        <v>4822.5</v>
       </c>
       <c r="L3">
-        <v>0.4698963792282039</v>
+        <v>0.4648371985425944</v>
       </c>
       <c r="M3">
-        <v>1931.3616</v>
+        <v>3356.1</v>
       </c>
       <c r="N3">
-        <v>0.03104144727960038</v>
+        <v>0.05154856110687868</v>
       </c>
       <c r="O3">
-        <v>0.4079508269437932</v>
+        <v>0.6959253499222395</v>
       </c>
       <c r="P3">
-        <v>1931.3616</v>
+        <v>2622.9</v>
       </c>
       <c r="Q3">
-        <v>0.03104144727960038</v>
+        <v>0.04028685704455531</v>
       </c>
       <c r="R3">
-        <v>0.4079508269437932</v>
+        <v>0.5438880248833593</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>733.2000000000003</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2184678644855637</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>35856.4</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.5507421788601903</v>
       </c>
       <c r="W3">
-        <v>0.1208994100972956</v>
+        <v>0.1126147163907246</v>
       </c>
       <c r="X3">
-        <v>0.0636039297479153</v>
+        <v>0.09652309518158698</v>
       </c>
       <c r="Y3">
-        <v>0.05729548034938034</v>
+        <v>0.01609162120913762</v>
       </c>
       <c r="Z3">
-        <v>0.08073510356725883</v>
+        <v>0.1173606578332634</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03888392699120916</v>
+        <v>0.06265241530131938</v>
       </c>
       <c r="AC3">
-        <v>-0.03888392699120916</v>
+        <v>-0.06265241530131938</v>
       </c>
       <c r="AD3">
-        <v>78847.39999999999</v>
+        <v>94264.60000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>78847.39999999999</v>
+        <v>94264.60000000001</v>
       </c>
       <c r="AG3">
-        <v>78847.39999999999</v>
+        <v>58408.2</v>
       </c>
       <c r="AH3">
-        <v>0.5589389945996985</v>
+        <v>0.5914819709079866</v>
       </c>
       <c r="AI3">
-        <v>0.6493607888449562</v>
+        <v>0.7005119447584185</v>
       </c>
       <c r="AJ3">
-        <v>0.5589389945996985</v>
+        <v>0.4728880497563835</v>
       </c>
       <c r="AK3">
-        <v>0.6493607888449562</v>
+        <v>0.5917217191155003</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0303</v>
+        <v>0.0584</v>
       </c>
       <c r="E4">
-        <v>0.0356</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="F4">
-        <v>0.214</v>
+        <v>0.171</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2760.7</v>
+        <v>3093.5</v>
       </c>
       <c r="L4">
-        <v>0.4324607985964253</v>
+        <v>0.4373798212871847</v>
       </c>
       <c r="M4">
-        <v>1220.633</v>
+        <v>1399.9656</v>
       </c>
       <c r="N4">
-        <v>0.03658708606095484</v>
+        <v>0.03651315810064316</v>
       </c>
       <c r="O4">
-        <v>0.4421461948056652</v>
+        <v>0.4525507030871181</v>
       </c>
       <c r="P4">
-        <v>1220.633</v>
+        <v>1399.9656</v>
       </c>
       <c r="Q4">
-        <v>0.03658708606095484</v>
+        <v>0.03651315810064316</v>
       </c>
       <c r="R4">
-        <v>0.4421461948056652</v>
+        <v>0.4525507030871181</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,49 +895,49 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.09399375576672307</v>
+        <v>0.1058547768957022</v>
       </c>
       <c r="X4">
-        <v>0.05490208263492685</v>
+        <v>0.0856614673326602</v>
       </c>
       <c r="Y4">
-        <v>0.03909167313179623</v>
+        <v>0.02019330956304197</v>
       </c>
       <c r="Z4">
-        <v>0.1146742928176101</v>
+        <v>0.120988807406305</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03913882164650584</v>
+        <v>0.06383850376674101</v>
       </c>
       <c r="AC4">
-        <v>-0.03913882164650584</v>
+        <v>-0.06383850376674101</v>
       </c>
       <c r="AD4">
-        <v>27482.5</v>
+        <v>36375.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>27482.5</v>
+        <v>36375.3</v>
       </c>
       <c r="AG4">
-        <v>27482.5</v>
+        <v>36375.3</v>
       </c>
       <c r="AH4">
-        <v>0.4516812419775528</v>
+        <v>0.4868429681717741</v>
       </c>
       <c r="AI4">
-        <v>0.4688270325504907</v>
+        <v>0.5512829062031129</v>
       </c>
       <c r="AJ4">
-        <v>0.4516812419775528</v>
+        <v>0.4868429681717741</v>
       </c>
       <c r="AK4">
-        <v>0.4688270325504907</v>
+        <v>0.5512829062031129</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06565</v>
+        <v>0.08845</v>
       </c>
       <c r="E2">
-        <v>0.07645</v>
+        <v>0.1005</v>
       </c>
       <c r="F2">
-        <v>0.1665</v>
+        <v>0.08660000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7916</v>
+        <v>11493.2</v>
       </c>
       <c r="L2">
-        <v>0.453706569460206</v>
+        <v>0.4865423203596618</v>
       </c>
       <c r="M2">
-        <v>4756.0656</v>
+        <v>5361.120000000001</v>
       </c>
       <c r="N2">
-        <v>0.04597586783570331</v>
+        <v>0.05290737321413241</v>
       </c>
       <c r="O2">
-        <v>0.6008167761495705</v>
+        <v>0.4664601677513661</v>
       </c>
       <c r="P2">
-        <v>4022.8656</v>
+        <v>5361.120000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03888818042089186</v>
+        <v>0.05290737321413241</v>
       </c>
       <c r="R2">
-        <v>0.5081942395149065</v>
+        <v>0.4664601677513661</v>
       </c>
       <c r="S2">
-        <v>733.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1541610359621617</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>35856.4</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.3466161415990797</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1092347466432134</v>
+        <v>0.1681713189551266</v>
       </c>
       <c r="X2">
-        <v>0.0910922812571236</v>
+        <v>0.07726756022929482</v>
       </c>
       <c r="Y2">
-        <v>0.0181424653860898</v>
+        <v>0.09090375872583178</v>
       </c>
       <c r="Z2">
-        <v>0.1188048830976402</v>
+        <v>0.1204265005391158</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06324545953403019</v>
+        <v>0.05467836455410523</v>
       </c>
       <c r="AC2">
-        <v>-0.06324545953403019</v>
+        <v>-0.05467836455410523</v>
       </c>
       <c r="AD2">
-        <v>130639.9</v>
+        <v>148129.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>130639.9</v>
+        <v>148129.7</v>
       </c>
       <c r="AG2">
-        <v>94783.5</v>
+        <v>148129.7</v>
       </c>
       <c r="AH2">
-        <v>0.5580829170705409</v>
+        <v>0.5938014110478634</v>
       </c>
       <c r="AI2">
-        <v>0.6514136494799508</v>
+        <v>0.6585716972315747</v>
       </c>
       <c r="AJ2">
-        <v>0.4781479136661614</v>
+        <v>0.5938014110478634</v>
       </c>
       <c r="AK2">
-        <v>0.5755201075462728</v>
+        <v>0.6585716972315747</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07290000000000001</v>
+        <v>0.0956</v>
       </c>
       <c r="E3">
-        <v>0.0901</v>
+        <v>0.134</v>
       </c>
       <c r="F3">
-        <v>0.162</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4822.5</v>
+        <v>7494.7</v>
       </c>
       <c r="L3">
-        <v>0.4648371985425944</v>
+        <v>0.5286967931263139</v>
       </c>
       <c r="M3">
-        <v>3356.1</v>
+        <v>3404.412</v>
       </c>
       <c r="N3">
-        <v>0.05154856110687868</v>
+        <v>0.05214884211106788</v>
       </c>
       <c r="O3">
-        <v>0.6959253499222395</v>
+        <v>0.4542425981026593</v>
       </c>
       <c r="P3">
-        <v>2622.9</v>
+        <v>3404.412</v>
       </c>
       <c r="Q3">
-        <v>0.04028685704455531</v>
+        <v>0.05214884211106788</v>
       </c>
       <c r="R3">
-        <v>0.5438880248833593</v>
+        <v>0.4542425981026593</v>
       </c>
       <c r="S3">
-        <v>733.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2184678644855637</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>35856.4</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.5507421788601903</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1126147163907246</v>
+        <v>0.1924718535563134</v>
       </c>
       <c r="X3">
-        <v>0.09652309518158698</v>
+        <v>0.08284840397760598</v>
       </c>
       <c r="Y3">
-        <v>0.01609162120913762</v>
+        <v>0.1096234495787075</v>
       </c>
       <c r="Z3">
-        <v>0.1173606578332634</v>
+        <v>0.1087681768796843</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06265241530131938</v>
+        <v>0.0540628223113335</v>
       </c>
       <c r="AC3">
-        <v>-0.06265241530131938</v>
+        <v>-0.0540628223113335</v>
       </c>
       <c r="AD3">
-        <v>94264.60000000001</v>
+        <v>112681.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>94264.60000000001</v>
+        <v>112681.1</v>
       </c>
       <c r="AG3">
-        <v>58408.2</v>
+        <v>112681.1</v>
       </c>
       <c r="AH3">
-        <v>0.5914819709079866</v>
+        <v>0.6331690114332305</v>
       </c>
       <c r="AI3">
-        <v>0.7005119447584185</v>
+        <v>0.7230512361629891</v>
       </c>
       <c r="AJ3">
-        <v>0.4728880497563835</v>
+        <v>0.6331690114332305</v>
       </c>
       <c r="AK3">
-        <v>0.5917217191155003</v>
+        <v>0.7230512361629891</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0584</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="E4">
-        <v>0.06280000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="F4">
-        <v>0.171</v>
+        <v>0.091</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3093.5</v>
+        <v>3998.5</v>
       </c>
       <c r="L4">
-        <v>0.4373798212871847</v>
+        <v>0.4232829437669377</v>
       </c>
       <c r="M4">
-        <v>1399.9656</v>
+        <v>1956.708</v>
       </c>
       <c r="N4">
-        <v>0.03651315810064316</v>
+        <v>0.05428107757221682</v>
       </c>
       <c r="O4">
-        <v>0.4525507030871181</v>
+        <v>0.4893605101913218</v>
       </c>
       <c r="P4">
-        <v>1399.9656</v>
+        <v>1956.708</v>
       </c>
       <c r="Q4">
-        <v>0.03651315810064316</v>
+        <v>0.05428107757221682</v>
       </c>
       <c r="R4">
-        <v>0.4525507030871181</v>
+        <v>0.4893605101913218</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,49 +895,49 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1058547768957022</v>
+        <v>0.1438707843539398</v>
       </c>
       <c r="X4">
-        <v>0.0856614673326602</v>
+        <v>0.07168671648098365</v>
       </c>
       <c r="Y4">
-        <v>0.02019330956304197</v>
+        <v>0.07218406787295611</v>
       </c>
       <c r="Z4">
-        <v>0.120988807406305</v>
+        <v>0.1435097479494592</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06383850376674101</v>
+        <v>0.05529390679687696</v>
       </c>
       <c r="AC4">
-        <v>-0.06383850376674101</v>
+        <v>-0.05529390679687696</v>
       </c>
       <c r="AD4">
-        <v>36375.3</v>
+        <v>35448.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>36375.3</v>
+        <v>35448.6</v>
       </c>
       <c r="AG4">
-        <v>36375.3</v>
+        <v>35448.6</v>
       </c>
       <c r="AH4">
-        <v>0.4868429681717741</v>
+        <v>0.4958102726994265</v>
       </c>
       <c r="AI4">
-        <v>0.5512829062031129</v>
+        <v>0.5131186979442596</v>
       </c>
       <c r="AJ4">
-        <v>0.4868429681717741</v>
+        <v>0.4958102726994265</v>
       </c>
       <c r="AK4">
-        <v>0.5512829062031129</v>
+        <v>0.5131186979442596</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08845</v>
+        <v>0.07544999999999999</v>
       </c>
       <c r="E2">
-        <v>0.1005</v>
+        <v>0.0873</v>
       </c>
       <c r="F2">
-        <v>0.08660000000000001</v>
+        <v>0.05995</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11493.2</v>
+        <v>10484.5</v>
       </c>
       <c r="L2">
-        <v>0.4865423203596618</v>
+        <v>0.4970606362300289</v>
       </c>
       <c r="M2">
-        <v>5361.120000000001</v>
+        <v>5275.6224</v>
       </c>
       <c r="N2">
-        <v>0.05290737321413241</v>
+        <v>0.05301035564496195</v>
       </c>
       <c r="O2">
-        <v>0.4664601677513661</v>
+        <v>0.5031830225571081</v>
       </c>
       <c r="P2">
-        <v>5361.120000000001</v>
+        <v>5275.6224</v>
       </c>
       <c r="Q2">
-        <v>0.05290737321413241</v>
+        <v>0.05301035564496195</v>
       </c>
       <c r="R2">
-        <v>0.4664601677513661</v>
+        <v>0.5031830225571081</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -645,49 +645,49 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1681713189551266</v>
+        <v>0.1511064255570131</v>
       </c>
       <c r="X2">
-        <v>0.07726756022929482</v>
+        <v>0.07287802589581707</v>
       </c>
       <c r="Y2">
-        <v>0.09090375872583178</v>
+        <v>0.07822839966119602</v>
       </c>
       <c r="Z2">
-        <v>0.1204265005391158</v>
+        <v>0.1590944746480658</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05467836455410523</v>
+        <v>0.06083839528074871</v>
       </c>
       <c r="AC2">
-        <v>-0.05467836455410523</v>
+        <v>-0.06083839528074871</v>
       </c>
       <c r="AD2">
-        <v>148129.7</v>
+        <v>69801</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>148129.7</v>
+        <v>69801</v>
       </c>
       <c r="AG2">
-        <v>148129.7</v>
+        <v>69801</v>
       </c>
       <c r="AH2">
-        <v>0.5938014110478634</v>
+        <v>0.4122391945268649</v>
       </c>
       <c r="AI2">
-        <v>0.6585716972315747</v>
+        <v>0.4583805607398078</v>
       </c>
       <c r="AJ2">
-        <v>0.5938014110478634</v>
+        <v>0.4122391945268649</v>
       </c>
       <c r="AK2">
-        <v>0.6585716972315747</v>
+        <v>0.4583805607398078</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DBS Group Holdings Ltd (SGX:D05)</t>
+          <t>United Overseas Bank Limited (SGX:U11)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0956</v>
+        <v>0.0735</v>
       </c>
       <c r="E3">
-        <v>0.134</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F3">
-        <v>0.08220000000000001</v>
+        <v>0.0789</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>7494.7</v>
+        <v>4619.7</v>
       </c>
       <c r="L3">
-        <v>0.5286967931263139</v>
+        <v>0.4424321942997241</v>
       </c>
       <c r="M3">
-        <v>3404.412</v>
+        <v>2256.525</v>
       </c>
       <c r="N3">
-        <v>0.05214884211106788</v>
+        <v>0.05071241558324812</v>
       </c>
       <c r="O3">
-        <v>0.4542425981026593</v>
+        <v>0.4884570426651081</v>
       </c>
       <c r="P3">
-        <v>3404.412</v>
+        <v>2256.525</v>
       </c>
       <c r="Q3">
-        <v>0.05214884211106788</v>
+        <v>0.05071241558324812</v>
       </c>
       <c r="R3">
-        <v>0.4542425981026593</v>
+        <v>0.4884570426651081</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,49 +770,49 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1924718535563134</v>
+        <v>0.1499737042014842</v>
       </c>
       <c r="X3">
-        <v>0.08284840397760598</v>
+        <v>0.07376501521944258</v>
       </c>
       <c r="Y3">
-        <v>0.1096234495787075</v>
+        <v>0.07620868898204165</v>
       </c>
       <c r="Z3">
-        <v>0.1087681768796843</v>
+        <v>0.1515291358648173</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0540628223113335</v>
+        <v>0.06073353816264038</v>
       </c>
       <c r="AC3">
-        <v>-0.0540628223113335</v>
+        <v>-0.06073353816264038</v>
       </c>
       <c r="AD3">
-        <v>112681.1</v>
+        <v>34291.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>112681.1</v>
+        <v>34291.6</v>
       </c>
       <c r="AG3">
-        <v>112681.1</v>
+        <v>34291.6</v>
       </c>
       <c r="AH3">
-        <v>0.6331690114332305</v>
+        <v>0.4352383164462653</v>
       </c>
       <c r="AI3">
-        <v>0.7230512361629891</v>
+        <v>0.4804622534575835</v>
       </c>
       <c r="AJ3">
-        <v>0.6331690114332305</v>
+        <v>0.4352383164462653</v>
       </c>
       <c r="AK3">
-        <v>0.7230512361629891</v>
+        <v>0.4804622534575835</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Overseas Bank Limited (SGX:U11)</t>
+          <t>Oversea-Chinese Banking Corporation Limited (SGX:O39)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08130000000000001</v>
+        <v>0.0774</v>
       </c>
       <c r="E4">
-        <v>0.067</v>
+        <v>0.106</v>
       </c>
       <c r="F4">
-        <v>0.091</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3998.5</v>
+        <v>5864.8</v>
       </c>
       <c r="L4">
-        <v>0.4232829437669377</v>
+        <v>0.5506130649492086</v>
       </c>
       <c r="M4">
-        <v>1956.708</v>
+        <v>3019.0974</v>
       </c>
       <c r="N4">
-        <v>0.05428107757221682</v>
+        <v>0.05486863756063252</v>
       </c>
       <c r="O4">
-        <v>0.4893605101913218</v>
+        <v>0.5147826694857455</v>
       </c>
       <c r="P4">
-        <v>1956.708</v>
+        <v>3019.0974</v>
       </c>
       <c r="Q4">
-        <v>0.05428107757221682</v>
+        <v>0.05486863756063252</v>
       </c>
       <c r="R4">
-        <v>0.4893605101913218</v>
+        <v>0.5147826694857455</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,49 +895,49 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1438707843539398</v>
+        <v>0.1522391469125419</v>
       </c>
       <c r="X4">
-        <v>0.07168671648098365</v>
+        <v>0.07199103657219155</v>
       </c>
       <c r="Y4">
-        <v>0.07218406787295611</v>
+        <v>0.08024811034035037</v>
       </c>
       <c r="Z4">
-        <v>0.1435097479494592</v>
+        <v>0.1672817848583553</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05529390679687696</v>
+        <v>0.06094325239885705</v>
       </c>
       <c r="AC4">
-        <v>-0.05529390679687696</v>
+        <v>-0.06094325239885705</v>
       </c>
       <c r="AD4">
-        <v>35448.6</v>
+        <v>35509.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>35448.6</v>
+        <v>35509.4</v>
       </c>
       <c r="AG4">
-        <v>35448.6</v>
+        <v>35509.4</v>
       </c>
       <c r="AH4">
-        <v>0.4958102726994265</v>
+        <v>0.3922238729310145</v>
       </c>
       <c r="AI4">
-        <v>0.5131186979442596</v>
+        <v>0.4389007889470776</v>
       </c>
       <c r="AJ4">
-        <v>0.4958102726994265</v>
+        <v>0.3922238729310145</v>
       </c>
       <c r="AK4">
-        <v>0.5131186979442596</v>
+        <v>0.4389007889470776</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07544999999999999</v>
+        <v>0.0774</v>
       </c>
       <c r="E2">
-        <v>0.0873</v>
+        <v>0.106</v>
       </c>
       <c r="F2">
-        <v>0.05995</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>10484.5</v>
+        <v>19026</v>
       </c>
       <c r="L2">
-        <v>0.4970606362300289</v>
+        <v>0.5056246960431798</v>
       </c>
       <c r="M2">
-        <v>5275.6224</v>
+        <v>9932.5664</v>
       </c>
       <c r="N2">
-        <v>0.05301035564496195</v>
+        <v>0.05214260388422398</v>
       </c>
       <c r="O2">
-        <v>0.5031830225571081</v>
+        <v>0.5220522653211395</v>
       </c>
       <c r="P2">
-        <v>5275.6224</v>
+        <v>9932.5664</v>
       </c>
       <c r="Q2">
-        <v>0.05301035564496195</v>
+        <v>0.05214260388422398</v>
       </c>
       <c r="R2">
-        <v>0.5031830225571081</v>
+        <v>0.5220522653211395</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -645,49 +645,49 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1511064255570131</v>
+        <v>0.1522391469125419</v>
       </c>
       <c r="X2">
-        <v>0.07287802589581707</v>
+        <v>0.07374703620104082</v>
       </c>
       <c r="Y2">
-        <v>0.07822839966119602</v>
+        <v>0.0784921107115011</v>
       </c>
       <c r="Z2">
-        <v>0.1590944746480658</v>
+        <v>0.1305256797247731</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06083839528074871</v>
+        <v>0.06072338430193916</v>
       </c>
       <c r="AC2">
-        <v>-0.06083839528074871</v>
+        <v>-0.06072338430193916</v>
       </c>
       <c r="AD2">
-        <v>69801</v>
+        <v>183600.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>69801</v>
+        <v>183600.7</v>
       </c>
       <c r="AG2">
-        <v>69801</v>
+        <v>183600.7</v>
       </c>
       <c r="AH2">
-        <v>0.4122391945268649</v>
+        <v>0.4907939069077643</v>
       </c>
       <c r="AI2">
-        <v>0.4583805607398078</v>
+        <v>0.5789223256949091</v>
       </c>
       <c r="AJ2">
-        <v>0.4122391945268649</v>
+        <v>0.4907939069077643</v>
       </c>
       <c r="AK2">
-        <v>0.4583805607398078</v>
+        <v>0.5789223256949091</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Overseas Bank Limited (SGX:U11)</t>
+          <t>DBS Group Holdings Ltd (SGX:D05)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0735</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="E3">
-        <v>0.06860000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="F3">
-        <v>0.0789</v>
+        <v>0.00191</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4619.7</v>
+        <v>8541.5</v>
       </c>
       <c r="L3">
-        <v>0.4424321942997241</v>
+        <v>0.5165490423749826</v>
       </c>
       <c r="M3">
-        <v>2256.525</v>
+        <v>4656.944</v>
       </c>
       <c r="N3">
-        <v>0.05071241558324812</v>
+        <v>0.05119326707552884</v>
       </c>
       <c r="O3">
-        <v>0.4884570426651081</v>
+        <v>0.5452138383187964</v>
       </c>
       <c r="P3">
-        <v>2256.525</v>
+        <v>4656.944</v>
       </c>
       <c r="Q3">
-        <v>0.05071241558324812</v>
+        <v>0.05119326707552884</v>
       </c>
       <c r="R3">
-        <v>0.4884570426651081</v>
+        <v>0.5452138383187964</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,49 +770,49 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1499737042014842</v>
+        <v>0.1985328811731372</v>
       </c>
       <c r="X3">
-        <v>0.07376501521944258</v>
+        <v>0.08054224036211913</v>
       </c>
       <c r="Y3">
-        <v>0.07620868898204165</v>
+        <v>0.1179906408110181</v>
       </c>
       <c r="Z3">
-        <v>0.1515291358648173</v>
+        <v>0.1061994474137499</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06073353816264038</v>
+        <v>0.05967478628863754</v>
       </c>
       <c r="AC3">
-        <v>-0.06073353816264038</v>
+        <v>-0.05967478628863754</v>
       </c>
       <c r="AD3">
-        <v>34291.6</v>
+        <v>113799.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34291.6</v>
+        <v>113799.7</v>
       </c>
       <c r="AG3">
-        <v>34291.6</v>
+        <v>113799.7</v>
       </c>
       <c r="AH3">
-        <v>0.4352383164462653</v>
+        <v>0.555750519125096</v>
       </c>
       <c r="AI3">
-        <v>0.4804622534575835</v>
+        <v>0.6902607469878349</v>
       </c>
       <c r="AJ3">
-        <v>0.4352383164462653</v>
+        <v>0.555750519125096</v>
       </c>
       <c r="AK3">
-        <v>0.4804622534575835</v>
+        <v>0.6902607469878349</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +829,245 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>United Overseas Bank Limited (SGX:U11)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0735</v>
+      </c>
+      <c r="E4">
+        <v>0.06860000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.0789</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>4619.7</v>
+      </c>
+      <c r="L4">
+        <v>0.4424321942997241</v>
+      </c>
+      <c r="M4">
+        <v>2256.525</v>
+      </c>
+      <c r="N4">
+        <v>0.05071241558324812</v>
+      </c>
+      <c r="O4">
+        <v>0.4884570426651081</v>
+      </c>
+      <c r="P4">
+        <v>2256.525</v>
+      </c>
+      <c r="Q4">
+        <v>0.05071241558324812</v>
+      </c>
+      <c r="R4">
+        <v>0.4884570426651081</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.1499737042014842</v>
+      </c>
+      <c r="X4">
+        <v>0.07374703620104082</v>
+      </c>
+      <c r="Y4">
+        <v>0.07622666800044341</v>
+      </c>
+      <c r="Z4">
+        <v>0.1515291358648173</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06072338430193916</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06072338430193916</v>
+      </c>
+      <c r="AD4">
+        <v>34291.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>34291.6</v>
+      </c>
+      <c r="AG4">
+        <v>34291.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.4352383164462653</v>
+      </c>
+      <c r="AI4">
+        <v>0.4804622534575835</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4352383164462653</v>
+      </c>
+      <c r="AK4">
+        <v>0.4804622534575835</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Oversea-Chinese Banking Corporation Limited (SGX:O39)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>0.0774</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>0.106</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>0.04099999999999999</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>5864.8</v>
       </c>
-      <c r="L4">
+      <c r="L5">
         <v>0.5506130649492086</v>
       </c>
-      <c r="M4">
+      <c r="M5">
         <v>3019.0974</v>
       </c>
-      <c r="N4">
+      <c r="N5">
         <v>0.05486863756063252</v>
       </c>
-      <c r="O4">
+      <c r="O5">
         <v>0.5147826694857455</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <v>3019.0974</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <v>0.05486863756063252</v>
       </c>
-      <c r="R4">
+      <c r="R5">
         <v>0.5147826694857455</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
         <v>0.1522391469125419</v>
       </c>
-      <c r="X4">
-        <v>0.07199103657219155</v>
-      </c>
-      <c r="Y4">
-        <v>0.08024811034035037</v>
-      </c>
-      <c r="Z4">
+      <c r="X5">
+        <v>0.0719741980643346</v>
+      </c>
+      <c r="Y5">
+        <v>0.08026494884820733</v>
+      </c>
+      <c r="Z5">
         <v>0.1672817848583553</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06094325239885705</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06094325239885705</v>
-      </c>
-      <c r="AD4">
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06093301835576612</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06093301835576612</v>
+      </c>
+      <c r="AD5">
         <v>35509.4</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>35509.4</v>
       </c>
-      <c r="AG4">
+      <c r="AG5">
         <v>35509.4</v>
       </c>
-      <c r="AH4">
+      <c r="AH5">
         <v>0.3922238729310145</v>
       </c>
-      <c r="AI4">
+      <c r="AI5">
         <v>0.4389007889470776</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ5">
         <v>0.3922238729310145</v>
       </c>
-      <c r="AK4">
+      <c r="AK5">
         <v>0.4389007889470776</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
